--- a/data/employees/EMP047/AST-EMP047-06.xlsx
+++ b/data/employees/EMP047/AST-EMP047-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Data Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,184 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Experiment Data Log - Riley Patel (R&amp;D)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Riley Patel | Role: Director | Location: Austin | Date: 2025-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>91</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Experiment ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Next Steps</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP-2026-041</t>
+          <t>EMP047</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low-temp deposition</t>
+          <t>Ast Emp047 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>68</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP disclosure</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP-2026-042</t>
+          <t>EMP047</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novel etchant blend</t>
+          <t>Ast Emp047 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP-2026-043</t>
+          <t>EMP047</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surface treatment A</t>
+          <t>Ast Emp047 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.51</v>
+        <v>89</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Redesign</t>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP-2026-044</t>
+          <t>EMP047</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plasma optimisation</t>
+          <t>Ast Emp047 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start Q3</t>
+          <t>Section 1: Automation backlog refinement. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>85</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>69</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>61</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>67</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>90</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>95</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>61</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>84</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp047 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>83</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP047</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP047 contributes to ast emp047 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>